--- a/ShelfMind-RPA/downloads/gvxVentasFueraRuta.xlsx
+++ b/ShelfMind-RPA/downloads/gvxVentasFueraRuta.xlsx
@@ -53,19 +53,19 @@
     <t>Sabado</t>
   </si>
   <si>
-    <t>2c23dac225e76266</t>
-  </si>
-  <si>
-    <t>FRANCO BONELLO</t>
-  </si>
-  <si>
-    <t>35209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COÑEQUIR MARIA SOLEDAD   </t>
-  </si>
-  <si>
-    <t>YAPEYU 532</t>
+    <t>2b32c57db9d924a4</t>
+  </si>
+  <si>
+    <t>lisandro acosta</t>
+  </si>
+  <si>
+    <t>3428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGNACIO ALBERTO LUQUE   </t>
+  </si>
+  <si>
+    <t>SAN MARTIN 619</t>
   </si>
   <si>
     <t>Sí</t>
@@ -74,19 +74,82 @@
     <t>No</t>
   </si>
   <si>
-    <t>d9252681b5a98896</t>
-  </si>
-  <si>
-    <t>Sandra-Ondarreta</t>
-  </si>
-  <si>
-    <t>35045</t>
-  </si>
-  <si>
-    <t>MARTIN MENDIBERRI</t>
-  </si>
-  <si>
-    <t>LAVALLE 348</t>
+    <t>3429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS FURRER   </t>
+  </si>
+  <si>
+    <t>SALTA 940</t>
+  </si>
+  <si>
+    <t>2b554b7a35696761</t>
+  </si>
+  <si>
+    <t>Ignacio LERF</t>
+  </si>
+  <si>
+    <t>2873</t>
+  </si>
+  <si>
+    <t>AUTOSERVICIO LOS LAURELES</t>
+  </si>
+  <si>
+    <t>CALLE 15 150</t>
+  </si>
+  <si>
+    <t>71053c36f5ad9750</t>
+  </si>
+  <si>
+    <t>villoslada rafa</t>
+  </si>
+  <si>
+    <t>2265</t>
+  </si>
+  <si>
+    <t>JOSE LUIS ACOSTA</t>
+  </si>
+  <si>
+    <t>BULEVAR SAN MART?N 336</t>
+  </si>
+  <si>
+    <t>b3542ecd172e9eee</t>
+  </si>
+  <si>
+    <t>CRISTIAN AYALA</t>
+  </si>
+  <si>
+    <t>3427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCEDES SILVA   </t>
+  </si>
+  <si>
+    <t>CÓRDOBA 35</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANTE CHAMORRO   </t>
+  </si>
+  <si>
+    <t>CALLE 9 60</t>
+  </si>
+  <si>
+    <t>bfdca891eeb2e79b</t>
+  </si>
+  <si>
+    <t>JORGE GUARI</t>
+  </si>
+  <si>
+    <t>3426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIOSCO HUGO   </t>
+  </si>
+  <si>
+    <t>CORTADA BARRETO 123</t>
   </si>
 </sst>
 </file>
@@ -452,10 +515,10 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="15.57" customWidth="1"/>
-    <col min="2" max="2" width="17.43" customWidth="1"/>
+    <col min="2" max="2" width="16.29" customWidth="1"/>
     <col min="3" max="3" width="6.14" customWidth="1"/>
-    <col min="4" max="4" width="26.14" customWidth="1"/>
-    <col min="5" max="5" width="13.71" customWidth="1"/>
+    <col min="4" max="4" width="28.43" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="8.29" customWidth="1"/>
     <col min="7" max="7" width="4.29" customWidth="1"/>
     <col min="8" max="8" width="11.57" customWidth="1"/>
@@ -531,7 +594,7 @@
         <v>46141</v>
       </c>
       <c r="G2" s="4">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c t="s" r="H2" s="5">
         <v>19</v>
@@ -543,13 +606,13 @@
         <v>20</v>
       </c>
       <c t="s" r="K2" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c t="s" r="L2" s="5">
         <v>20</v>
       </c>
       <c t="s" r="M2" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c t="s" r="N2" s="5">
         <v>20</v>
@@ -557,34 +620,34 @@
     </row>
     <row r="3" ht="13.5" customHeight="1">
       <c t="s" r="A3" s="2">
+        <v>14</v>
+      </c>
+      <c t="s" r="B3" s="2">
+        <v>15</v>
+      </c>
+      <c t="s" r="C3" s="2">
         <v>21</v>
       </c>
-      <c t="s" r="B3" s="2">
+      <c t="s" r="D3" s="2">
         <v>22</v>
       </c>
-      <c t="s" r="C3" s="2">
+      <c t="s" r="E3" s="2">
         <v>23</v>
-      </c>
-      <c t="s" r="D3" s="2">
-        <v>24</v>
-      </c>
-      <c t="s" r="E3" s="2">
-        <v>25</v>
       </c>
       <c r="F3" s="3">
         <v>46141</v>
       </c>
       <c r="G3" s="4">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c t="s" r="H3" s="5">
         <v>19</v>
       </c>
       <c t="s" r="I3" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c t="s" r="J3" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c t="s" r="K3" s="5">
         <v>20</v>
@@ -596,6 +659,226 @@
         <v>20</v>
       </c>
       <c t="s" r="N3" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1">
+      <c t="s" r="A4" s="2">
+        <v>24</v>
+      </c>
+      <c t="s" r="B4" s="2">
+        <v>25</v>
+      </c>
+      <c t="s" r="C4" s="2">
+        <v>26</v>
+      </c>
+      <c t="s" r="D4" s="2">
+        <v>27</v>
+      </c>
+      <c t="s" r="E4" s="2">
+        <v>28</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46141</v>
+      </c>
+      <c r="G4" s="4">
+        <v>43</v>
+      </c>
+      <c t="s" r="H4" s="5">
+        <v>19</v>
+      </c>
+      <c t="s" r="I4" s="5">
+        <v>19</v>
+      </c>
+      <c t="s" r="J4" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="K4" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="L4" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="M4" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="N4" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="13.5" customHeight="1">
+      <c t="s" r="A5" s="2">
+        <v>29</v>
+      </c>
+      <c t="s" r="B5" s="2">
+        <v>30</v>
+      </c>
+      <c t="s" r="C5" s="2">
+        <v>31</v>
+      </c>
+      <c t="s" r="D5" s="2">
+        <v>32</v>
+      </c>
+      <c t="s" r="E5" s="2">
+        <v>33</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46141</v>
+      </c>
+      <c r="G5" s="4">
+        <v>30</v>
+      </c>
+      <c t="s" r="H5" s="5">
+        <v>19</v>
+      </c>
+      <c t="s" r="I5" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="J5" s="5">
+        <v>19</v>
+      </c>
+      <c t="s" r="K5" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="L5" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="M5" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="N5" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="13.5" customHeight="1">
+      <c t="s" r="A6" s="2">
+        <v>34</v>
+      </c>
+      <c t="s" r="B6" s="2">
+        <v>35</v>
+      </c>
+      <c t="s" r="C6" s="2">
+        <v>36</v>
+      </c>
+      <c t="s" r="D6" s="2">
+        <v>37</v>
+      </c>
+      <c t="s" r="E6" s="2">
+        <v>38</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46141</v>
+      </c>
+      <c r="G6" s="4">
+        <v>16</v>
+      </c>
+      <c t="s" r="H6" s="5">
+        <v>19</v>
+      </c>
+      <c t="s" r="I6" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="J6" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="K6" s="5">
+        <v>19</v>
+      </c>
+      <c t="s" r="L6" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="M6" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="N6" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" ht="13.5" customHeight="1">
+      <c t="s" r="A7" s="2">
+        <v>34</v>
+      </c>
+      <c t="s" r="B7" s="2">
+        <v>35</v>
+      </c>
+      <c t="s" r="C7" s="2">
+        <v>39</v>
+      </c>
+      <c t="s" r="D7" s="2">
+        <v>40</v>
+      </c>
+      <c t="s" r="E7" s="2">
+        <v>41</v>
+      </c>
+      <c r="F7" s="3">
+        <v>46141</v>
+      </c>
+      <c r="G7" s="4">
+        <v>16</v>
+      </c>
+      <c t="s" r="H7" s="5">
+        <v>19</v>
+      </c>
+      <c t="s" r="I7" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="J7" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="K7" s="5">
+        <v>19</v>
+      </c>
+      <c t="s" r="L7" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="M7" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="N7" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" ht="13.5" customHeight="1">
+      <c t="s" r="A8" s="2">
+        <v>42</v>
+      </c>
+      <c t="s" r="B8" s="2">
+        <v>43</v>
+      </c>
+      <c t="s" r="C8" s="2">
+        <v>44</v>
+      </c>
+      <c t="s" r="D8" s="2">
+        <v>45</v>
+      </c>
+      <c t="s" r="E8" s="2">
+        <v>46</v>
+      </c>
+      <c r="F8" s="3">
+        <v>46141</v>
+      </c>
+      <c r="G8" s="4">
+        <v>16</v>
+      </c>
+      <c t="s" r="H8" s="5">
+        <v>19</v>
+      </c>
+      <c t="s" r="I8" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="J8" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="K8" s="5">
+        <v>19</v>
+      </c>
+      <c t="s" r="L8" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="M8" s="5">
+        <v>20</v>
+      </c>
+      <c t="s" r="N8" s="5">
         <v>20</v>
       </c>
     </row>
@@ -603,7 +886,7 @@
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:N3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:N8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>